--- a/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>LEVI</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45256</v>
+      </c>
+      <c r="E7" s="2">
         <v>44892</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44528</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44164</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43793</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43429</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43065</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42701</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42337</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41973</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41602</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41238</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6179000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6168600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5763900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4452600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5763100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5575400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4904000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4552700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4494500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4754000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4681700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4610200</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2663300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2619800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2417200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2099700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2661700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2577500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2341300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2223700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2225500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2405600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2331200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2410900</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3515700</v>
+      </c>
+      <c r="E10" s="3">
         <v>3548800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3346700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2352900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3101400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2998000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2562700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2329000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2269000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2348400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2350500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2199300</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,9 +899,12 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,48 +941,54 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>134500</v>
+      </c>
+      <c r="E14" s="3">
         <v>53600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>50200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>188900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>24900</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>30000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>58800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>176400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8200</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,9 +1025,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5844700</v>
+      </c>
+      <c r="E17" s="3">
         <v>5509600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5114200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4552500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5221300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5035000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4446800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4090500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4077400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4460500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4216900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4284400</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>334300</v>
+      </c>
+      <c r="E18" s="3">
         <v>659000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>649700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-99900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>541800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>540400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>457300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>462200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>417000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>293500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>464800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>325800</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E20" s="3">
         <v>16300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-39900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>18200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-25400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-22100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4800</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>476400</v>
+      </c>
+      <c r="E21" s="3">
         <v>834200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>796300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>34200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>667800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>675500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>534800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>584300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>493700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>380900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>567400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>453200</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E22" s="3">
         <v>25700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>72900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>82200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>66200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>55300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>68600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>73200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>81200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>117600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>129000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>134700</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>265200</v>
+      </c>
+      <c r="E23" s="3">
         <v>649600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>580200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-189800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>477600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>500000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>348800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>407300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>310400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>153900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>322600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>195900</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E24" s="3">
         <v>80500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-62600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>82600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>81700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>116100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>49500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>94500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>54900</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>249600</v>
+      </c>
+      <c r="E26" s="3">
         <v>569100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>553500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-127100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>395000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>418300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>284600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>291200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>209900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>104300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>228100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>141000</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>249600</v>
+      </c>
+      <c r="E27" s="3">
         <v>569100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>553500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-127100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>394600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>416200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>281400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>291100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>209400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>106100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>229200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>143900</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1481,11 +1541,11 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>-133100</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>39900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-18200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>25400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>22100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4800</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>249600</v>
+      </c>
+      <c r="E33" s="3">
         <v>569100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>553500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-127100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>394600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>283100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>281400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>291100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>209400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>106100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>229200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>143900</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>249600</v>
+      </c>
+      <c r="E35" s="3">
         <v>569100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>553500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-127100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>394600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>283100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>281400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>291100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>209400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>106100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>229200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>143900</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45256</v>
+      </c>
+      <c r="E38" s="2">
         <v>44892</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44528</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44164</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43793</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43429</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43065</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42701</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42337</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41973</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41602</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41238</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,64 +1900,68 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>398800</v>
+      </c>
+      <c r="E41" s="3">
         <v>429600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>810300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1497200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>934200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>713100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>633600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>375600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>318600</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="M41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>489300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>406100</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>70600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>91500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>96500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>80700</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -1889,168 +1978,183 @@
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>752700</v>
+      </c>
+      <c r="E43" s="3">
         <v>697000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>707600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>540200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>782800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>534200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>485500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>479000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>498200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>780200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>446700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>500700</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1290100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1416800</v>
       </c>
-      <c r="E44" s="3">
-        <v>897900</v>
-      </c>
       <c r="F44" s="3">
+        <v>898000</v>
+      </c>
+      <c r="G44" s="3">
         <v>817700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>884200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>883800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>759400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>716200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>606900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>600900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>603900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>518900</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E45" s="3">
         <v>213900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>202500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>174600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>188200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>157000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>118700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>115400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>277400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>299900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>252700</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2637600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2827900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2709900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3126200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2870200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2288100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1997200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1686100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1528100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1658500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1839700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1678400</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2087,87 +2191,96 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1714600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1592800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1606300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1443300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>529600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>460600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1800200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>393600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>390800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>392100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1655700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>458800</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>571300</v>
+      </c>
+      <c r="E49" s="3">
         <v>652400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>678200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>312200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>278600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>279100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>323100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>277200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>278400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>284800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>339500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>299900</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1130100</v>
+      </c>
+      <c r="E52" s="3">
         <v>964700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>905700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>759500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>554100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>514900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>655900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>630100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>687000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>588700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>557500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>733000</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6053600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6037800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5900100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5641200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4232400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3542700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3357800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2987100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2884400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2924100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3127400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3170100</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,242 +2524,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>567900</v>
+      </c>
+      <c r="E57" s="3">
         <v>657200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>524800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>375400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>360300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>351300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>289500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>270300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>238300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>234900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>254500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>225700</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E58" s="3">
         <v>11700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>31900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>38500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>38900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>147600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>131500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>61500</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1207100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1312700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1338900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1155800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>799300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>668900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>551100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>452500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>460300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>514600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>489100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>509600</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1787500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1981600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1869600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1548900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1167200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1052200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>879100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>761700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>846200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>881000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>785500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>796900</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1009400</v>
+      </c>
+      <c r="E61" s="3">
         <v>984500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1020700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1546700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1006700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1020200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1055400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1021600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1017300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1104100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1514300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1669700</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1210300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1168000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1344100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1246200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>486900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>503600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>594000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>612600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>620300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>706900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>614200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>797100</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4007200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4134100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4234400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4341800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2668900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2583400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2533900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2398200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2485300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2693200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2917200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3269100</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1750200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1699400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1474900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1114300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1310500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1084300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1100900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>935000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>705700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>528200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>476000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>274000</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2046400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1903700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1665700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1299500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1563500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>959300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>823900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>588900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>399100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>230900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>210200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-99000</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45256</v>
+      </c>
+      <c r="E80" s="2">
         <v>44892</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44528</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44164</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43793</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43429</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43065</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42701</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42337</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41973</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41602</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41238</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>249600</v>
+      </c>
+      <c r="E81" s="3">
         <v>569100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>553500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-127100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>394600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>283100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>281400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>291100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>209400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>106100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>229200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>143900</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>165300</v>
+      </c>
+      <c r="E83" s="3">
         <v>158900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>143200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>141800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>123900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>120200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>117400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>103900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>102000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>109500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>115700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>122600</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>435500</v>
+      </c>
+      <c r="E89" s="3">
         <v>228100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>737300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>469600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>412200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>420400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>525900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>306600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>218300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>232900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>411300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>531000</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-315500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-267100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-166900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-130400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-175400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-159400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-118600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-103000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-102300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-73400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-91800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-83900</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-240700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-235700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-571800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-188600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-243300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-179400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-124400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-80800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-71800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-92800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-75200</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,26 +3987,27 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-190500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-174300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-104400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-63600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-113900</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -3788,14 +4021,17 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-25100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-20000</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-214100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-365400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-840900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>286000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>55000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-148600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-151800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-173500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-94900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-341700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-230500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-250900</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-22300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3200</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-380600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-687100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>562900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>221100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>79000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>258100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>57000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-191000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>83100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>201600</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
@@ -2039,7 +2039,7 @@
         <v>1416800</v>
       </c>
       <c r="F44" s="3">
-        <v>898000</v>
+        <v>897900</v>
       </c>
       <c r="G44" s="3">
         <v>817700</v>

--- a/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>LEVI</t>
   </si>
@@ -768,13 +768,13 @@
         <v>2663300</v>
       </c>
       <c r="E9" s="3">
-        <v>2619800</v>
+        <v>2616400</v>
       </c>
       <c r="F9" s="3">
         <v>2417200</v>
       </c>
       <c r="G9" s="3">
-        <v>2099700</v>
+        <v>2057400</v>
       </c>
       <c r="H9" s="3">
         <v>2661700</v>
@@ -810,13 +810,13 @@
         <v>3515700</v>
       </c>
       <c r="E10" s="3">
-        <v>3548800</v>
+        <v>3552200</v>
       </c>
       <c r="F10" s="3">
         <v>3346700</v>
       </c>
       <c r="G10" s="3">
-        <v>2352900</v>
+        <v>2395200</v>
       </c>
       <c r="H10" s="3">
         <v>3101400</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>134500</v>
+        <v>179100</v>
       </c>
       <c r="E14" s="3">
-        <v>53600</v>
+        <v>46500</v>
       </c>
       <c r="F14" s="3">
-        <v>50200</v>
+        <v>36500</v>
       </c>
       <c r="G14" s="3">
-        <v>188900</v>
-      </c>
-      <c r="H14" s="3">
-        <v>24900</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>171000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
-        <v>30000</v>
+        <v>22800</v>
       </c>
       <c r="K14" s="3">
         <v>7500</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>164900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>158600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>143200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>141800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>123900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>117400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5844700</v>
+        <v>5624200</v>
       </c>
       <c r="E17" s="3">
-        <v>5509600</v>
+        <v>5456200</v>
       </c>
       <c r="F17" s="3">
-        <v>5114200</v>
+        <v>5077700</v>
       </c>
       <c r="G17" s="3">
-        <v>4552500</v>
+        <v>4381400</v>
       </c>
       <c r="H17" s="3">
-        <v>5221300</v>
+        <v>5212400</v>
       </c>
       <c r="I17" s="3">
-        <v>5035000</v>
+        <v>5038400</v>
       </c>
       <c r="J17" s="3">
-        <v>4446800</v>
+        <v>4436900</v>
       </c>
       <c r="K17" s="3">
         <v>4090500</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>334300</v>
+        <v>554800</v>
       </c>
       <c r="E18" s="3">
-        <v>659000</v>
+        <v>712400</v>
       </c>
       <c r="F18" s="3">
-        <v>649700</v>
+        <v>686200</v>
       </c>
       <c r="G18" s="3">
-        <v>-99900</v>
+        <v>71200</v>
       </c>
       <c r="H18" s="3">
-        <v>541800</v>
+        <v>550700</v>
       </c>
       <c r="I18" s="3">
-        <v>540400</v>
+        <v>537100</v>
       </c>
       <c r="J18" s="3">
-        <v>457300</v>
+        <v>467200</v>
       </c>
       <c r="K18" s="3">
         <v>462200</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-23200</v>
+        <v>64600</v>
       </c>
       <c r="E20" s="3">
-        <v>16300</v>
+        <v>-9400</v>
       </c>
       <c r="F20" s="3">
-        <v>3500</v>
+        <v>-3400</v>
       </c>
       <c r="G20" s="3">
-        <v>-7700</v>
+        <v>7700</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>25600</v>
       </c>
       <c r="I20" s="3">
-        <v>14900</v>
+        <v>-8100</v>
       </c>
       <c r="J20" s="3">
-        <v>-39900</v>
+        <v>31000</v>
       </c>
       <c r="K20" s="3">
         <v>18200</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>476400</v>
+        <v>655100</v>
       </c>
       <c r="E21" s="3">
-        <v>834200</v>
+        <v>880400</v>
       </c>
       <c r="F21" s="3">
-        <v>796300</v>
+        <v>832800</v>
       </c>
       <c r="G21" s="3">
-        <v>34200</v>
+        <v>205300</v>
       </c>
       <c r="H21" s="3">
-        <v>667800</v>
+        <v>649100</v>
       </c>
       <c r="I21" s="3">
-        <v>675500</v>
+        <v>665400</v>
       </c>
       <c r="J21" s="3">
-        <v>534800</v>
+        <v>553600</v>
       </c>
       <c r="K21" s="3">
         <v>584300</v>
@@ -1287,7 +1287,7 @@
         <v>580200</v>
       </c>
       <c r="G23" s="3">
-        <v>-189800</v>
+        <v>-189700</v>
       </c>
       <c r="H23" s="3">
         <v>477600</v>
@@ -1335,7 +1335,7 @@
         <v>82600</v>
       </c>
       <c r="I24" s="3">
-        <v>81700</v>
+        <v>214800</v>
       </c>
       <c r="J24" s="3">
         <v>64200</v>
@@ -1419,7 +1419,7 @@
         <v>395000</v>
       </c>
       <c r="I26" s="3">
-        <v>418300</v>
+        <v>285200</v>
       </c>
       <c r="J26" s="3">
         <v>284600</v>
@@ -1461,7 +1461,7 @@
         <v>394600</v>
       </c>
       <c r="I27" s="3">
-        <v>416200</v>
+        <v>283100</v>
       </c>
       <c r="J27" s="3">
         <v>281400</v>
@@ -1529,26 +1529,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-133100</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>23200</v>
+        <v>-64600</v>
       </c>
       <c r="E32" s="3">
-        <v>-16300</v>
+        <v>9400</v>
       </c>
       <c r="F32" s="3">
-        <v>-3500</v>
+        <v>3400</v>
       </c>
       <c r="G32" s="3">
-        <v>7700</v>
+        <v>-7700</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>-25600</v>
       </c>
       <c r="I32" s="3">
-        <v>-14900</v>
+        <v>8100</v>
       </c>
       <c r="J32" s="3">
-        <v>39900</v>
+        <v>-31000</v>
       </c>
       <c r="K32" s="3">
         <v>-18200</v>
@@ -1963,11 +1963,11 @@
       <c r="H42" s="3">
         <v>80700</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -2039,7 +2039,7 @@
         <v>1416800</v>
       </c>
       <c r="F44" s="3">
-        <v>897900</v>
+        <v>898000</v>
       </c>
       <c r="G44" s="3">
         <v>817700</v>
@@ -2158,26 +2158,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>460600</v>
       </c>
       <c r="J48" s="3">
-        <v>1800200</v>
+        <v>424500</v>
       </c>
       <c r="K48" s="3">
         <v>393600</v>
@@ -2261,7 +2261,7 @@
         <v>279100</v>
       </c>
       <c r="J49" s="3">
-        <v>323100</v>
+        <v>280200</v>
       </c>
       <c r="K49" s="3">
         <v>277200</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1130100</v>
+        <v>400600</v>
       </c>
       <c r="E52" s="3">
-        <v>964700</v>
+        <v>339700</v>
       </c>
       <c r="F52" s="3">
-        <v>905700</v>
+        <v>332600</v>
       </c>
       <c r="G52" s="3">
-        <v>759500</v>
+        <v>261900</v>
       </c>
       <c r="H52" s="3">
-        <v>554100</v>
+        <v>146200</v>
       </c>
       <c r="I52" s="3">
-        <v>514900</v>
+        <v>117100</v>
       </c>
       <c r="J52" s="3">
-        <v>655900</v>
+        <v>118000</v>
       </c>
       <c r="K52" s="3">
         <v>630100</v>
@@ -2540,7 +2540,7 @@
         <v>524800</v>
       </c>
       <c r="G57" s="3">
-        <v>375400</v>
+        <v>375500</v>
       </c>
       <c r="H57" s="3">
         <v>360300</v>
@@ -2573,16 +2573,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12500</v>
+        <v>258000</v>
       </c>
       <c r="E58" s="3">
-        <v>11700</v>
+        <v>247400</v>
       </c>
       <c r="F58" s="3">
-        <v>5900</v>
+        <v>251300</v>
       </c>
       <c r="G58" s="3">
-        <v>17600</v>
+        <v>254800</v>
       </c>
       <c r="H58" s="3">
         <v>7600</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1207100</v>
+        <v>316900</v>
       </c>
       <c r="E59" s="3">
-        <v>1312700</v>
+        <v>303700</v>
       </c>
       <c r="F59" s="3">
-        <v>1338900</v>
+        <v>328500</v>
       </c>
       <c r="G59" s="3">
-        <v>1155800</v>
+        <v>273000</v>
       </c>
       <c r="H59" s="3">
-        <v>799300</v>
+        <v>216600</v>
       </c>
       <c r="I59" s="3">
-        <v>668900</v>
+        <v>15500</v>
       </c>
       <c r="J59" s="3">
-        <v>551100</v>
+        <v>16000</v>
       </c>
       <c r="K59" s="3">
         <v>452500</v>
@@ -2699,16 +2699,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1009400</v>
+        <v>1922500</v>
       </c>
       <c r="E61" s="3">
-        <v>984500</v>
+        <v>1843600</v>
       </c>
       <c r="F61" s="3">
-        <v>1020700</v>
+        <v>1990200</v>
       </c>
       <c r="G61" s="3">
-        <v>1546700</v>
+        <v>2405000</v>
       </c>
       <c r="H61" s="3">
         <v>1006700</v>
@@ -2717,7 +2717,7 @@
         <v>1020200</v>
       </c>
       <c r="J61" s="3">
-        <v>1055400</v>
+        <v>1038900</v>
       </c>
       <c r="K61" s="3">
         <v>1021600</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1210300</v>
+        <v>50300</v>
       </c>
       <c r="E62" s="3">
-        <v>1168000</v>
+        <v>54600</v>
       </c>
       <c r="F62" s="3">
-        <v>1344100</v>
+        <v>59400</v>
       </c>
       <c r="G62" s="3">
-        <v>1246200</v>
+        <v>64300</v>
       </c>
       <c r="H62" s="3">
-        <v>486900</v>
+        <v>144700</v>
       </c>
       <c r="I62" s="3">
-        <v>503600</v>
+        <v>425400</v>
       </c>
       <c r="J62" s="3">
-        <v>594000</v>
+        <v>242700</v>
       </c>
       <c r="K62" s="3">
         <v>612600</v>
@@ -2921,13 +2921,13 @@
         <v>4341800</v>
       </c>
       <c r="H66" s="3">
-        <v>2668900</v>
+        <v>2660900</v>
       </c>
       <c r="I66" s="3">
-        <v>2583400</v>
+        <v>2875200</v>
       </c>
       <c r="J66" s="3">
-        <v>2533900</v>
+        <v>2655500</v>
       </c>
       <c r="K66" s="3">
         <v>2398200</v>
@@ -3320,10 +3320,10 @@
         <v>1563500</v>
       </c>
       <c r="I76" s="3">
-        <v>959300</v>
+        <v>660100</v>
       </c>
       <c r="J76" s="3">
-        <v>823900</v>
+        <v>696900</v>
       </c>
       <c r="K76" s="3">
         <v>588900</v>
@@ -3496,16 +3496,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>165300</v>
+        <v>160900</v>
       </c>
       <c r="E83" s="3">
-        <v>158900</v>
+        <v>154600</v>
       </c>
       <c r="F83" s="3">
-        <v>143200</v>
+        <v>142100</v>
       </c>
       <c r="G83" s="3">
-        <v>141800</v>
+        <v>136600</v>
       </c>
       <c r="H83" s="3">
         <v>123900</v>
@@ -3811,7 +3811,7 @@
         <v>-315500</v>
       </c>
       <c r="E91" s="3">
-        <v>-267100</v>
+        <v>-268300</v>
       </c>
       <c r="F91" s="3">
         <v>-166900</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-190500</v>
+        <v>190500</v>
       </c>
       <c r="E96" s="3">
-        <v>-174300</v>
+        <v>174300</v>
       </c>
       <c r="F96" s="3">
-        <v>-104400</v>
+        <v>104400</v>
       </c>
       <c r="G96" s="3">
-        <v>-63600</v>
+        <v>63600</v>
       </c>
       <c r="H96" s="3">
-        <v>-113900</v>
+        <v>113900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>-11600</v>
       </c>
       <c r="G101" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="H101" s="3">
         <v>-2800</v>
@@ -4252,10 +4252,10 @@
         <v>-380600</v>
       </c>
       <c r="F102" s="3">
-        <v>-687100</v>
+        <v>-687000</v>
       </c>
       <c r="G102" s="3">
-        <v>562900</v>
+        <v>562800</v>
       </c>
       <c r="H102" s="3">
         <v>221100</v>

--- a/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>LEVI</t>
   </si>
@@ -656,195 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45627</v>
+      </c>
+      <c r="E7" s="2">
         <v>45256</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44892</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44528</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44164</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43793</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43429</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43065</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42701</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42337</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41973</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41602</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41238</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6355300</v>
+      </c>
+      <c r="E8" s="3">
         <v>6179000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6168600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5763900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4452600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5763100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5575400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4904000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4552700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4494500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4754000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4681700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4610200</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2539400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2663300</v>
       </c>
-      <c r="E9" s="3">
-        <v>2616400</v>
-      </c>
       <c r="F9" s="3">
+        <v>2619800</v>
+      </c>
+      <c r="G9" s="3">
         <v>2417200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2057400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2661700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2577500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2341300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2223700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2225500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2405600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2331200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2410900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3815900</v>
+      </c>
+      <c r="E10" s="3">
         <v>3515700</v>
       </c>
-      <c r="E10" s="3">
-        <v>3552200</v>
-      </c>
       <c r="F10" s="3">
+        <v>3548800</v>
+      </c>
+      <c r="G10" s="3">
         <v>3346700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2395200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3101400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2998000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2562700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2329000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2269000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2348400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2350500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2199300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,78 +961,84 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>179100</v>
+        <v>374900</v>
       </c>
       <c r="E14" s="3">
-        <v>46500</v>
+        <v>217100</v>
       </c>
       <c r="F14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G14" s="3">
         <v>36500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>171000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>22800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>58800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>176400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>192900</v>
+      </c>
+      <c r="E15" s="3">
         <v>164900</v>
       </c>
-      <c r="E15" s="3">
-        <v>158600</v>
-      </c>
       <c r="F15" s="3">
+        <v>158900</v>
+      </c>
+      <c r="G15" s="3">
         <v>143200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>141800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>123900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>120200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>117400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1028,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5701800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5624200</v>
       </c>
-      <c r="E17" s="3">
-        <v>5456200</v>
-      </c>
       <c r="F17" s="3">
+        <v>5501400</v>
+      </c>
+      <c r="G17" s="3">
         <v>5077700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4381400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5212400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5038400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4436900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4090500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4077400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4460500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4216900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4284400</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>653500</v>
+      </c>
+      <c r="E18" s="3">
         <v>554800</v>
       </c>
-      <c r="E18" s="3">
-        <v>712400</v>
-      </c>
       <c r="F18" s="3">
+        <v>667200</v>
+      </c>
+      <c r="G18" s="3">
         <v>686200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>71200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>550700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>537100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>467200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>462200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>417000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>293500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>464800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>325800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>64600</v>
+        <v>17800</v>
       </c>
       <c r="E20" s="3">
+        <v>26600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-9400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>25600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>31000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-22100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>655100</v>
+        <v>828600</v>
       </c>
       <c r="E21" s="3">
-        <v>880400</v>
+        <v>693100</v>
       </c>
       <c r="F21" s="3">
+        <v>835500</v>
+      </c>
+      <c r="G21" s="3">
         <v>832800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>205300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>649100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>665400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>553600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>584300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>493700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>380900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>567400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>453200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E22" s="3">
         <v>45900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>72900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>82200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>55300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>68600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>73200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>81200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>117600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>129000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>134700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E23" s="3">
         <v>265200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>649600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>580200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-189700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>477600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>500000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>348800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>407300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>310400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>153900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>322600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>195900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E24" s="3">
         <v>15600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>80500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-62600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>82600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>214800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>64200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>116100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>49500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>94500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>54900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E26" s="3">
         <v>249600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>569100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>553500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-127100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>395000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>285200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>284600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>291200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>209900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>104300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>228100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>141000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E27" s="3">
         <v>249600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>569100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>553500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-127100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>394600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>283100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>281400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>291100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>209400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>106100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>229200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>143900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1611,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1565,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-64600</v>
+        <v>-17800</v>
       </c>
       <c r="E32" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="F32" s="3">
         <v>9400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-25600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-31000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>22100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E33" s="3">
         <v>249600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>569100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>553500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-127100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>394600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>283100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>281400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>291100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>209400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>106100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>229200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>143900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E35" s="3">
         <v>249600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>569100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>553500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-127100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>394600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>283100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>281400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>291100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>209400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>106100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>229200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>143900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45627</v>
+      </c>
+      <c r="E38" s="2">
         <v>45256</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44892</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44528</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44164</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43793</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43429</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43065</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42701</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42337</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41973</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41602</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41238</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>690000</v>
+      </c>
+      <c r="E41" s="3">
         <v>398800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>429600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>810300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1497200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>934200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>713100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>633600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>375600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>318600</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="N41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>489300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>406100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1952,25 +2042,25 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>70600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>91500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>96500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>80700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
@@ -1981,180 +2071,195 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>710000</v>
+      </c>
+      <c r="E43" s="3">
         <v>752700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>697000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>707600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>540200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>782800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>534200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>485500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>479000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>498200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>780200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>446700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>500700</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1239400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1290100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1416800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>898000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>817700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>884200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>883800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>759400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>716200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>606900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>600900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>603900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>518900</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E45" s="3">
         <v>196000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>213900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>202500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>174600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>188200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>157000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>118700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>115400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>104500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>277400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>299900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>252700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2851100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2637600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2827900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2709900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3126200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2870200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2288100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1997200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1686100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1528100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1658500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1839700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1678400</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2179,8 +2284,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2194,93 +2299,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1787300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1714600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1592800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1606300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1443300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>529600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>460600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>424500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>393600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>390800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>392100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1655700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>458800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>474200</v>
+      </c>
+      <c r="E49" s="3">
         <v>571300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>652400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>678200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>312200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>278600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>279100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>280200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>277200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>278400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>284800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>339500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>299900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>464400</v>
+      </c>
+      <c r="E52" s="3">
         <v>400600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>339700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>332600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>261900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>146200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>117100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>118000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>630100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>687000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>588700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>557500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>733000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6375500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6053600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6037800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5900100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5641200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4232400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3542700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3357800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2987100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2884400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2924100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3127400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3170100</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>663400</v>
+      </c>
+      <c r="E57" s="3">
         <v>567900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>657200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>524800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>375500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>360300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>351300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>289500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>270300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>238300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>234900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>254500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>225700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>258800</v>
+      </c>
+      <c r="E58" s="3">
         <v>258000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>247400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>251300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>254800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>31900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>38500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>38900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>147600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>131500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>42500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>61500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>378400</v>
+      </c>
+      <c r="E59" s="3">
         <v>316900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>303700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>328500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>273000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>216600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>452500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>460300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>514600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>489100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>509600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2010500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1787500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1981600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1869600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1548900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1167200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1052200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>879100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>761700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>846200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>881000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>785500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>796900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1954500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1922500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1843600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1990200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2405000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1006700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1020200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1038900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1021600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1017300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1104100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1514300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1669700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>186400</v>
+      </c>
+      <c r="E62" s="3">
         <v>50300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>54600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>59400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>144700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>425400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>242700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>612600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>620300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>706900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>614200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>797100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4405000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4007200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4134100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4234400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4341800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2660900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2875200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2655500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2398200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2485300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2693200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2917200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3269100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1672000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1750200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1699400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1474900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1114300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1310500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1084300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1100900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>935000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>705700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>528200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>476000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>274000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1970500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2046400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1903700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1665700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1299500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1563500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>660100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>696900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>588900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>399100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>230900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>210200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-99000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45627</v>
+      </c>
+      <c r="E80" s="2">
         <v>45256</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44892</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44528</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44164</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43793</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43429</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43065</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42701</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42337</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41973</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41602</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41238</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E81" s="3">
         <v>249600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>569100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>553500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-127100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>394600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>283100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>281400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>291100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>209400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>106100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>229200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>143900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>188400</v>
+      </c>
+      <c r="E83" s="3">
         <v>160900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>154600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>142100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>136600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>123900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>120200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>117400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>103900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>102000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>109500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>115700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>122600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>898400</v>
+      </c>
+      <c r="E89" s="3">
         <v>435500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>228100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>737300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>469600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>412200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>420400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>525900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>306600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>218300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>232900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>411300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>531000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-315500</v>
+        <v>-227500</v>
       </c>
       <c r="E91" s="3">
-        <v>-268300</v>
+        <v>-313600</v>
       </c>
       <c r="F91" s="3">
+        <v>-267100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-166900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-130400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-175400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-159400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-118600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-103000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-102300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-73400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-91800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-83900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-281100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-240700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-235700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-571800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-188600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-243300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-179400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-124400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-80800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-71800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-92800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-75200</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,35 +4221,36 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>198500</v>
+      </c>
+      <c r="E96" s="3">
         <v>190500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>174300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>104400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>63600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>113900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>90000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>70000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4024,14 +4258,17 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-25100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-20000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-319300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-214100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-365400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-840900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>286000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>55000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-148600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-151800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-173500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-94900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-341700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-230500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-250900</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G101" s="3">
         <v>-11600</v>
       </c>
-      <c r="E101" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-11600</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-22300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-10400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3200</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-30900</v>
+        <v>291200</v>
       </c>
       <c r="E102" s="3">
-        <v>-380600</v>
+        <v>-30800</v>
       </c>
       <c r="F102" s="3">
+        <v>-380700</v>
+      </c>
+      <c r="G102" s="3">
         <v>-687000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>562800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>221100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>79000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>258100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>57000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-191000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>83100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>201600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEVI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>LEVI</t>
   </si>
@@ -656,208 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E7" s="2">
         <v>45627</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45256</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44892</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44528</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44164</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43793</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43429</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43065</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42701</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42337</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41973</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41602</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41238</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6355300</v>
+        <v>6282000</v>
       </c>
       <c r="E8" s="3">
-        <v>6179000</v>
+        <v>6032000</v>
       </c>
       <c r="F8" s="3">
+        <v>5842100</v>
+      </c>
+      <c r="G8" s="3">
         <v>6168600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5763900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4452600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5763100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5575400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4904000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4552700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4494500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4754000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4681700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4610200</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2539400</v>
+        <v>2404200</v>
       </c>
       <c r="E9" s="3">
-        <v>2663300</v>
+        <v>2374900</v>
       </c>
       <c r="F9" s="3">
+        <v>2481400</v>
+      </c>
+      <c r="G9" s="3">
         <v>2619800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2417200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2057400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2661700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2577500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2341300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2223700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2225500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2405600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2331200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2410900</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3815900</v>
+        <v>3877800</v>
       </c>
       <c r="E10" s="3">
-        <v>3515700</v>
+        <v>3657100</v>
       </c>
       <c r="F10" s="3">
+        <v>3360700</v>
+      </c>
+      <c r="G10" s="3">
         <v>3548800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3346700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2395200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3101400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2998000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2562700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2329000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2269000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2348400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2350500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2199300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,84 +981,90 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>374900</v>
+        <v>33200</v>
       </c>
       <c r="E14" s="3">
-        <v>217100</v>
+        <v>371800</v>
       </c>
       <c r="F14" s="3">
+        <v>189700</v>
+      </c>
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>36500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>171000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>22800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>58800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>176400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8200</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E15" s="3">
         <v>192900</v>
       </c>
-      <c r="E15" s="3">
-        <v>164900</v>
-      </c>
       <c r="F15" s="3">
+        <v>165300</v>
+      </c>
+      <c r="G15" s="3">
         <v>158900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>143200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>141800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>123900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>120200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>117400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5701800</v>
+        <v>5563300</v>
       </c>
       <c r="E17" s="3">
-        <v>5624200</v>
+        <v>5383000</v>
       </c>
       <c r="F17" s="3">
+        <v>5313600</v>
+      </c>
+      <c r="G17" s="3">
         <v>5501400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5077700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4381400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5212400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5038400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4436900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4090500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4077400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4460500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4216900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4284400</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>653500</v>
+        <v>718700</v>
       </c>
       <c r="E18" s="3">
-        <v>554800</v>
+        <v>649000</v>
       </c>
       <c r="F18" s="3">
+        <v>528500</v>
+      </c>
+      <c r="G18" s="3">
         <v>667200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>686200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>71200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>550700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>537100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>467200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>462200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>417000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>293500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>464800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>325800</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>17800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>26600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>25600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>31000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>18200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-25400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-22100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>828600</v>
+        <v>921800</v>
       </c>
       <c r="E21" s="3">
-        <v>693100</v>
+        <v>824100</v>
       </c>
       <c r="F21" s="3">
+        <v>667200</v>
+      </c>
+      <c r="G21" s="3">
         <v>835500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>832800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>205300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>649100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>665400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>553600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>584300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>493700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>380900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>567400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>453200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E22" s="3">
         <v>41800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>45900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>72900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>82200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>66200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>55300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>68600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>73200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>81200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>117600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>129000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>134700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>219000</v>
+        <v>634000</v>
       </c>
       <c r="E23" s="3">
-        <v>265200</v>
+        <v>217600</v>
       </c>
       <c r="F23" s="3">
+        <v>266300</v>
+      </c>
+      <c r="G23" s="3">
         <v>649600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>580200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-189700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>477600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>500000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>348800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>407300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>310400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>153900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>322600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>195900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>8400</v>
+        <v>132000</v>
       </c>
       <c r="E24" s="3">
-        <v>15600</v>
+        <v>7200</v>
       </c>
       <c r="F24" s="3">
+        <v>15700</v>
+      </c>
+      <c r="G24" s="3">
         <v>80500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-62600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>82600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>214800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>116100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>49500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>94500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>54900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>210600</v>
+        <v>502000</v>
       </c>
       <c r="E26" s="3">
-        <v>249600</v>
+        <v>210400</v>
       </c>
       <c r="F26" s="3">
+        <v>250600</v>
+      </c>
+      <c r="G26" s="3">
         <v>569100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>553500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-127100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>395000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>285200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>284600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>291200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>209900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>104300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>228100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>141000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E27" s="3">
         <v>210600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>249600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>569100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>553500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-127100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>394600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>283100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>281400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>291100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>209400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>106100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>229200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>143900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,20 +1642,23 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>76100</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1614,8 +1675,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1629,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-17800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-26600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-25600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-31000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-18200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>25400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>22100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E33" s="3">
         <v>210600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>249600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>569100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>553500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-127100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>394600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>283100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>281400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>291100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>209400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>106100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>229200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>143900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E35" s="3">
         <v>210600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>249600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>569100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>553500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-127100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>394600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>283100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>281400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>291100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>209400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>106100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>229200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>143900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E38" s="2">
         <v>45627</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45256</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44892</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44528</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44164</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43793</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43429</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43065</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42701</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42337</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41973</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41602</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41238</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,82 +2074,86 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>757900</v>
+      </c>
+      <c r="E41" s="3">
         <v>690000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>398800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>429600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>810300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1497200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>934200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>713100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>633600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>375600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>318600</v>
       </c>
-      <c r="N41" s="3" t="s">
+      <c r="O41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>489300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>406100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>90900</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>70600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>91500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>96500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>80700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
@@ -2074,192 +2164,207 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>774700</v>
+      </c>
+      <c r="E43" s="3">
         <v>710000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>752700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>697000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>707600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>540200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>782800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>534200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>485500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>479000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>498200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>780200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>446700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>500700</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1239400</v>
+        <v>1237700</v>
       </c>
       <c r="E44" s="3">
+        <v>1131300</v>
+      </c>
+      <c r="F44" s="3">
         <v>1290100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1416800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>898000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>817700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>884200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>883800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>759400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>716200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>606900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>600900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>603900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>518900</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>211700</v>
+        <v>292500</v>
       </c>
       <c r="E45" s="3">
+        <v>319800</v>
+      </c>
+      <c r="F45" s="3">
         <v>196000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>213900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>202500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>174600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>188200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>157000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>118700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>115400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>104500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>277400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>299900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>252700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3153700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2851100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2637600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2827900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2709900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3126200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2870200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2288100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1997200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1686100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1528100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1658500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1839700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1678400</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2287,8 +2392,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2302,99 +2407,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1787300</v>
+        <v>1830000</v>
       </c>
       <c r="E48" s="3">
+        <v>1752900</v>
+      </c>
+      <c r="F48" s="3">
         <v>1714600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1592800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1606300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1443300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>529600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>460600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>424500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>393600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>390800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>392100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1655700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>458800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>475000</v>
+      </c>
+      <c r="E49" s="3">
         <v>474200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>571300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>652400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>678200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>312200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>278600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>279100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>280200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>277200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>278400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>284800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>339500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>299900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>464400</v>
+        <v>560000</v>
       </c>
       <c r="E52" s="3">
+        <v>498800</v>
+      </c>
+      <c r="F52" s="3">
         <v>400600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>339700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>332600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>261900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>146200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>117100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>118000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>630100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>687000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>588700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>557500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>733000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6848800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6375500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6053600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6037800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5900100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5641200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4232400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3542700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3357800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2987100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2884400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2924100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3127400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3170100</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>597600</v>
+      </c>
+      <c r="E57" s="3">
         <v>663400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>567900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>657200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>524800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>375500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>360300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>351300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>289500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>270300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>238300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>234900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>254500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>225700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>258800</v>
+        <v>260700</v>
       </c>
       <c r="E58" s="3">
+        <v>252900</v>
+      </c>
+      <c r="F58" s="3">
         <v>258000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>247400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>251300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>254800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>31900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>38500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>38900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>147600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>131500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>42500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>61500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>402300</v>
+      </c>
+      <c r="E59" s="3">
         <v>378400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>316900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>303700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>328500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>273000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>216600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>452500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>460300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>514600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>489100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>509600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2032500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2010500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1787500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1981600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1869600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1548900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1167200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1052200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>879100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>761700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>846200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>881000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>785500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>796900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1954500</v>
+        <v>2044800</v>
       </c>
       <c r="E61" s="3">
+        <v>1937000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1922500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1843600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1990200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2405000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1006700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1020200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1038900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1021600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1017300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1104100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1514300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1669700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>186400</v>
+        <v>240200</v>
       </c>
       <c r="E62" s="3">
+        <v>203900</v>
+      </c>
+      <c r="F62" s="3">
         <v>50300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>54600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>59400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>64300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>144700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>425400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>242700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>612600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>620300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>706900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>614200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>797100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4570200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4405000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4007200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4134100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4234400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4341800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2660900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2875200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2655500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2398200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2485300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2693200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2917200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3269100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1897300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1672000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1750200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1699400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1474900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1114300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1310500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1084300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1100900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>935000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>705700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>528200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>476000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>274000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2278600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1970500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2046400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1903700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1665700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1299500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1563500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>660100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>696900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>588900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>399100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>230900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>210200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-99000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E80" s="2">
         <v>45627</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45256</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44892</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44528</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44164</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43793</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43429</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43065</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42701</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42337</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41973</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41602</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41238</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E81" s="3">
         <v>210600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>249600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>569100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>553500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-127100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>394600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>283100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>281400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>291100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>209400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>106100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>229200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>143900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>188400</v>
+        <v>206000</v>
       </c>
       <c r="E83" s="3">
-        <v>160900</v>
+        <v>192900</v>
       </c>
       <c r="F83" s="3">
+        <v>165300</v>
+      </c>
+      <c r="G83" s="3">
         <v>154600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>142100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>136600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>123900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>120200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>117400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>103900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>102000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>109500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>115700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>122600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>529600</v>
+      </c>
+      <c r="E89" s="3">
         <v>898400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>435500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>228100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>737300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>469600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>412200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>420400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>525900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>306600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>218300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>232900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>411300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>531000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-221400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-227500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-313600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-267100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-166900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-130400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-175400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-159400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-118600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-103000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-102300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-73400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-91800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-83900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-281100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-240700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-235700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-571800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-188600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-243300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-179400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-124400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-68300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-80800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-71800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-92800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-75200</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,38 +4455,39 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E96" s="3">
         <v>198500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>190500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>174300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>104400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>63600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>113900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>90000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>70000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4261,14 +4495,17 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-25100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-319300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-214100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-365400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-840900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>286000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>55000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-148600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-151800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-173500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-94900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-341700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-230500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-250900</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-11600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-22300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-10400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E102" s="3">
         <v>291200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-380700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-687000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>562800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>221100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>79000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>258100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>57000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-191000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>83100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>201600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
